--- a/assessment_forms/017_delegate_health_assessment--assessment_forms.xlsx
+++ b/assessment_forms/017_delegate_health_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'patient_information',_'label':_'patient_information'}</t>
+          <t>patient_information</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'patient_information', 'label': 'Patient Information'}</t>
+          <t>Patient Information</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medical_history',_'label':_'medical_history'}</t>
+          <t>medical_history</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'medical_history', 'label': 'Medical History'}</t>
+          <t>Medical History</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'medications',_'label':_'medications'}</t>
+          <t>medications</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'medications', 'label': 'Medications'}</t>
+          <t>Medications</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'allergies',_'label':_'allergies'}</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'allergies', 'label': 'Allergies'}</t>
+          <t>Allergies</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'medical_conditions',_'label':_'medical_conditions'}</t>
+          <t>medical_conditions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'medical_conditions', 'label': 'Medical Conditions'}</t>
+          <t>Medical Conditions</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'medical_procedures',_'label':_'medical_procedures'}</t>
+          <t>medical_procedures</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'medical_procedures', 'label': 'Medical Procedures'}</t>
+          <t>Medical Procedures</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'medical_devices',_'label':_'medical_devices'}</t>
+          <t>medical_devices</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'medical_devices', 'label': 'Medical Devices'}</t>
+          <t>Medical Devices</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'medical_history_additional_info',_'label':_'additional_medical_history'}</t>
+          <t>additional_medical_history</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'medical_history_additional_info', 'label': 'Additional Medical History'}</t>
+          <t>Additional Medical History</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'patient_questionnaire_1',_'label':_'patient_questionnaire_1'}</t>
+          <t>patient_questionnaire_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'patient_questionnaire_1', 'label': 'Patient Questionnaire 1'}</t>
+          <t>Patient Questionnaire 1</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'patient_questionnaire_2',_'label':_'patient_questionnaire_2'}</t>
+          <t>patient_questionnaire_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'patient_questionnaire_2', 'label': 'Patient Questionnaire 2'}</t>
+          <t>Patient Questionnaire 2</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'patient_questionnaire_3',_'label':_'patient_questionnaire_3'}</t>
+          <t>patient_questionnaire_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'patient_questionnaire_3', 'label': 'Patient Questionnaire 3'}</t>
+          <t>Patient Questionnaire 3</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'patient_questionnaire_4',_'label':_'patient_questionnaire_4'}</t>
+          <t>patient_questionnaire_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'patient_questionnaire_4', 'label': 'Patient Questionnaire 4'}</t>
+          <t>Patient Questionnaire 4</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'patient_questionnaire_5',_'label':_'patient_questionnaire_5'}</t>
+          <t>patient_questionnaire_5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'patient_questionnaire_5', 'label': 'Patient Questionnaire 5'}</t>
+          <t>Patient Questionnaire 5</t>
         </is>
       </c>
     </row>
@@ -938,12 +938,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'patient_questionnaire_6',_'label':_'patient_questionnaire_6'}</t>
+          <t>patient_questionnaire_6</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'patient_questionnaire_6', 'label': 'Patient Questionnaire 6'}</t>
+          <t>Patient Questionnaire 6</t>
         </is>
       </c>
     </row>
@@ -955,12 +955,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'patient_questionnaire_7',_'label':_'patient_questionnaire_7'}</t>
+          <t>patient_questionnaire_7</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'patient_questionnaire_7', 'label': 'Patient Questionnaire 7'}</t>
+          <t>Patient Questionnaire 7</t>
         </is>
       </c>
     </row>
@@ -972,12 +972,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'patient_questionnaire_8',_'label':_'patient_questionnaire_8'}</t>
+          <t>patient_questionnaire_8</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'patient_questionnaire_8', 'label': 'Patient Questionnaire 8'}</t>
+          <t>Patient Questionnaire 8</t>
         </is>
       </c>
     </row>
@@ -989,12 +989,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'patient_questionnaire_9',_'label':_'patient_questionnaire_9'}</t>
+          <t>patient_questionnaire_9</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'patient_questionnaire_9', 'label': 'Patient Questionnaire 9'}</t>
+          <t>Patient Questionnaire 9</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'patient_questionnaire_10',_'label':_'patient_questionnaire_10'}</t>
+          <t>patient_questionnaire_10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'patient_questionnaire_10', 'label': 'Patient Questionnaire 10'}</t>
+          <t>Patient Questionnaire 10</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'delegate_questionnaire_1',_'label':_'delegate_questionnaire_1'}</t>
+          <t>delegate_questionnaire_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'delegate_questionnaire_1', 'label': 'Delegate Questionnaire 1'}</t>
+          <t>Delegate Questionnaire 1</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'delegate_questionnaire_2',_'label':_'delegate_questionnaire_2'}</t>
+          <t>delegate_questionnaire_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'delegate_questionnaire_2', 'label': 'Delegate Questionnaire 2'}</t>
+          <t>Delegate Questionnaire 2</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'delegate_questionnaire_3',_'label':_'delegate_questionnaire_3'}</t>
+          <t>delegate_questionnaire_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'delegate_questionnaire_3', 'label': 'Delegate Questionnaire 3'}</t>
+          <t>Delegate Questionnaire 3</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'delegate_questionnaire_4',_'label':_'delegate_questionnaire_4'}</t>
+          <t>delegate_questionnaire_4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'delegate_questionnaire_4', 'label': 'Delegate Questionnaire 4'}</t>
+          <t>Delegate Questionnaire 4</t>
         </is>
       </c>
     </row>
@@ -1091,12 +1091,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'delegate_questionnaire_5',_'label':_'delegate_questionnaire_5'}</t>
+          <t>delegate_questionnaire_5</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'delegate_questionnaire_5', 'label': 'Delegate Questionnaire 5'}</t>
+          <t>Delegate Questionnaire 5</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_6,_'name':_'delegate_questionnaire_6',_'label':_'delegate_questionnaire_6'}</t>
+          <t>delegate_questionnaire_6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 6, 'name': 'delegate_questionnaire_6', 'label': 'Delegate Questionnaire 6'}</t>
+          <t>Delegate Questionnaire 6</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_7,_'name':_'delegate_questionnaire_7',_'label':_'delegate_questionnaire_7'}</t>
+          <t>delegate_questionnaire_7</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 7, 'name': 'delegate_questionnaire_7', 'label': 'Delegate Questionnaire 7'}</t>
+          <t>Delegate Questionnaire 7</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_8,_'name':_'delegate_questionnaire_8',_'label':_'delegate_questionnaire_8'}</t>
+          <t>delegate_questionnaire_8</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 8, 'name': 'delegate_questionnaire_8', 'label': 'Delegate Questionnaire 8'}</t>
+          <t>Delegate Questionnaire 8</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_9,_'name':_'delegate_questionnaire_9',_'label':_'delegate_questionnaire_9'}</t>
+          <t>delegate_questionnaire_9</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 9, 'name': 'delegate_questionnaire_9', 'label': 'Delegate Questionnaire 9'}</t>
+          <t>Delegate Questionnaire 9</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'delegate_questionnaire_10',_'label':_'delegate_questionnaire_10'}</t>
+          <t>delegate_questionnaire_10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'delegate_questionnaire_10', 'label': 'Delegate Questionnaire 10'}</t>
+          <t>Delegate Questionnaire 10</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'medical_history_2_option_1',_'label':_'option_1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'medical_history_2_option_1', 'label': 'Option 1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'medical_history_2_option_2',_'label':_'option_2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'medical_history_2_option_2', 'label': 'Option 2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'medical_history_2_option_3',_'label':_'option_3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'medical_history_2_option_3', 'label': 'Option 3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
